--- a/data/trans_camb/IP12-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 9,33</t>
+          <t>-2,44; 10,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 6,69</t>
+          <t>-5,64; 5,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 6,2</t>
+          <t>-6,33; 6,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 6,77</t>
+          <t>-4,24; 6,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 3,03</t>
+          <t>-7,02; 3,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 8,35</t>
+          <t>-4,29; 9,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 6,91</t>
+          <t>-1,3; 6,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 3,17</t>
+          <t>-4,24; 3,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 5,8</t>
+          <t>-4,09; 5,14</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 162,26</t>
+          <t>-22,57; 177,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 129,48</t>
+          <t>-49,74; 97,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 100,54</t>
+          <t>-59,58; 118,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 135,9</t>
+          <t>-42,2; 136,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 58,51</t>
+          <t>-64,72; 68,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-52,62; 177,88</t>
+          <t>-49,87; 170,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 124,27</t>
+          <t>-14,89; 106,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 58,24</t>
+          <t>-42,3; 54,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 98,67</t>
+          <t>-44,08; 77,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 6,23</t>
+          <t>-1,51; 6,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,05</t>
+          <t>0,63; 8,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 6,53</t>
+          <t>-1,96; 6,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,6</t>
+          <t>-2,65; 5,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 3,16</t>
+          <t>-4,48; 3,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,93</t>
+          <t>-3,17; 5,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 4,76</t>
+          <t>-1,06; 4,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,48</t>
+          <t>-0,79; 4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 4,63</t>
+          <t>-1,62; 4,45</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,25; 131,57</t>
+          <t>-20,39; 134,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,89; 190,11</t>
+          <t>6,31; 184,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 138,29</t>
+          <t>-26,38; 127,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 88,44</t>
+          <t>-28,42; 82,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 55,36</t>
+          <t>-45,25; 46,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 93,85</t>
+          <t>-35,5; 92,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 78,32</t>
+          <t>-12,41; 78,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 75,47</t>
+          <t>-9,88; 72,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,89; 77,92</t>
+          <t>-19,66; 78,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 5,82</t>
+          <t>-4,96; 5,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 2,76</t>
+          <t>-7,37; 2,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 5,43</t>
+          <t>-5,68; 5,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,7</t>
+          <t>-5,41; 4,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 5,53</t>
+          <t>-4,44; 5,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,5</t>
+          <t>-5,15; 4,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 3,29</t>
+          <t>-3,79; 3,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,63</t>
+          <t>-4,37; 2,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 3,4</t>
+          <t>-3,15; 3,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,91; 115,89</t>
+          <t>-44,99; 110,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 53,2</t>
+          <t>-63,6; 44,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,87; 109,29</t>
+          <t>-48,68; 102,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 82,68</t>
+          <t>-58,74; 88,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,58; 140,27</t>
+          <t>-46,78; 113,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,05; 101,75</t>
+          <t>-53,81; 102,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 57,77</t>
+          <t>-39,72; 64,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 46,1</t>
+          <t>-45,79; 45,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,35; 60,52</t>
+          <t>-34,18; 63,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,1</t>
+          <t>-2,1; 5,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 4,42</t>
+          <t>-2,54; 5,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,38</t>
+          <t>-1,98; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 9,32</t>
+          <t>0,75; 8,52</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 4,57</t>
+          <t>-2,69; 4,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 7,62</t>
+          <t>0,16; 7,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,55</t>
+          <t>0,41; 5,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,53</t>
+          <t>-1,78; 3,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,07</t>
+          <t>-0,02; 5,0</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,27; 193,42</t>
+          <t>-41,23; 209,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,66; 168,37</t>
+          <t>-47,36; 210,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 177,34</t>
+          <t>-34,22; 179,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 367,8</t>
+          <t>4,77; 352,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,55; 199,32</t>
+          <t>-53,45; 214,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,54; 330,45</t>
+          <t>-4,26; 323,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 187,98</t>
+          <t>5,42; 191,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 120,76</t>
+          <t>-36,52; 131,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 172,56</t>
+          <t>-3,19; 182,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,46</t>
+          <t>-0,31; 4,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,77</t>
+          <t>-0,9; 3,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,31</t>
+          <t>-1,53; 3,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,17</t>
+          <t>-0,51; 3,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,97</t>
+          <t>-2,04; 2,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,56</t>
+          <t>-1,06; 3,86</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,88</t>
+          <t>0,36; 3,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,3</t>
+          <t>-0,68; 2,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,66</t>
+          <t>-0,58; 2,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 80,85</t>
+          <t>-5,0; 81,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 69,18</t>
+          <t>-13,17; 66,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 59,9</t>
+          <t>-21,57; 57,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 71,89</t>
+          <t>-7,28; 69,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 34,06</t>
+          <t>-26,39; 38,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 62,95</t>
+          <t>-13,37; 67,73</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,62; 67,37</t>
+          <t>5,84; 64,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 41,49</t>
+          <t>-9,77; 42,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 47,48</t>
+          <t>-8,73; 44,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores que en las últimas 2 semanas limitaron su actividad por dolores o síntomas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 10,16</t>
+          <t>-3,3; 9,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 5,83</t>
+          <t>-6,26; 5,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,46</t>
+          <t>-7,16; 6,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 6,9</t>
+          <t>-4,4; 6,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 3,31</t>
+          <t>-7,34; 3,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 9,65</t>
+          <t>-5,11; 8,67</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 6,57</t>
+          <t>-1,58; 6,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 3,43</t>
+          <t>-4,87; 3,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 5,14</t>
+          <t>-4,18; 5,25</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 177,9</t>
+          <t>-27,69; 180,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 97,86</t>
+          <t>-48,87; 94,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 118,15</t>
+          <t>-64,47; 125,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,2; 136,03</t>
+          <t>-41,85; 141,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,72; 68,87</t>
+          <t>-65,2; 70,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,87; 170,41</t>
+          <t>-50,39; 183,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 106,86</t>
+          <t>-16,24; 108,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 54,56</t>
+          <t>-47,47; 48,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 77,22</t>
+          <t>-44,48; 85,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,36</t>
+          <t>-1,56; 6,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 8,93</t>
+          <t>0,8; 9,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,16</t>
+          <t>-1,84; 6,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,11</t>
+          <t>-2,83; 5,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 3,05</t>
+          <t>-4,63; 3,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 5,45</t>
+          <t>-3,69; 5,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,73</t>
+          <t>-1,27; 4,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,48</t>
+          <t>-0,92; 4,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,45</t>
+          <t>-1,65; 4,57</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; 134,14</t>
+          <t>-21,36; 132,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,31; 184,89</t>
+          <t>7,75; 191,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 127,32</t>
+          <t>-24,97; 139,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,42; 82,24</t>
+          <t>-27,91; 91,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 46,34</t>
+          <t>-47,67; 53,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 92,76</t>
+          <t>-37,64; 86,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 78,84</t>
+          <t>-14,86; 78,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 72,72</t>
+          <t>-12,02; 75,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 78,01</t>
+          <t>-20,49; 72,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 5,8</t>
+          <t>-4,5; 6,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,4</t>
+          <t>-7,11; 3,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,43</t>
+          <t>-5,28; 5,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,01</t>
+          <t>-5,67; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 5,23</t>
+          <t>-4,71; 5,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 4,55</t>
+          <t>-4,76; 4,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 3,65</t>
+          <t>-3,53; 3,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,58</t>
+          <t>-4,31; 3,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,77</t>
+          <t>-3,71; 3,64</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,99; 110,27</t>
+          <t>-41,86; 115,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,6; 44,96</t>
+          <t>-61,11; 65,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-48,68; 102,03</t>
+          <t>-46,36; 99,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 88,12</t>
+          <t>-57,12; 112,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,78; 113,43</t>
+          <t>-47,77; 112,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 102,35</t>
+          <t>-51,41; 107,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 64,29</t>
+          <t>-37,01; 64,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,79; 45,47</t>
+          <t>-44,17; 56,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 63,26</t>
+          <t>-38,03; 63,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,44</t>
+          <t>-2,33; 4,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,05</t>
+          <t>-2,42; 4,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 4,59</t>
+          <t>-1,94; 4,47</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,75; 8,52</t>
+          <t>0,99; 8,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 4,87</t>
+          <t>-2,2; 4,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 7,71</t>
+          <t>0,06; 7,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,76</t>
+          <t>0,19; 5,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,52</t>
+          <t>-1,61; 3,44</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 5,0</t>
+          <t>-0,08; 5,23</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 209,55</t>
+          <t>-42,22; 222,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 210,81</t>
+          <t>-45,99; 176,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 179,74</t>
+          <t>-34,64; 182,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 352,07</t>
+          <t>12,43; 363,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,45; 214,91</t>
+          <t>-45,43; 196,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 323,71</t>
+          <t>-3,24; 327,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,42; 191,68</t>
+          <t>1,94; 189,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 131,29</t>
+          <t>-34,39; 119,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 182,02</t>
+          <t>-2,92; 178,38</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,41</t>
+          <t>-0,17; 4,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 3,59</t>
+          <t>-0,62; 3,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,14</t>
+          <t>-1,82; 2,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,95</t>
+          <t>-0,38; 4,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,14</t>
+          <t>-2,21; 2,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,86</t>
+          <t>-0,89; 3,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,67</t>
+          <t>0,44; 3,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,37</t>
+          <t>-0,8; 2,22</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,63</t>
+          <t>-0,74; 2,56</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 81,05</t>
+          <t>-2,67; 84,31</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 66,76</t>
+          <t>-10,06; 71,9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-21,57; 57,45</t>
+          <t>-23,69; 48,84</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 69,01</t>
+          <t>-5,66; 72,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,39; 38,65</t>
+          <t>-28,86; 35,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 67,73</t>
+          <t>-11,73; 68,18</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,84; 64,64</t>
+          <t>6,13; 61,11</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 42,04</t>
+          <t>-10,75; 38,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-8,73; 44,17</t>
+          <t>-10,59; 43,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP12-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP12-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,72</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,64</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,72</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,78</t>
+          <t>-3,84; 6,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,4</t>
+          <t>-6,25; 3,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 6,44</t>
+          <t>-5,18; 8,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 6,56</t>
+          <t>-2,47; 9,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 3,27</t>
+          <t>-5,19; 6,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 8,67</t>
+          <t>-6,57; 6,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 6,71</t>
+          <t>-1,25; 6,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,02</t>
+          <t>-4,45; 3,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 5,25</t>
+          <t>-4,11; 5,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-22,46%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>42,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,78%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-7,51%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-22,46%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>-7,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 180,27</t>
+          <t>-40,43; 135,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 94,47</t>
+          <t>-64,66; 58,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,47; 125,73</t>
+          <t>-52,29; 174,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 141,59</t>
+          <t>-22,03; 162,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,2; 70,14</t>
+          <t>-44,96; 129,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,39; 183,05</t>
+          <t>-61,16; 108,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 108,22</t>
+          <t>-13,02; 124,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,47; 48,04</t>
+          <t>-43,53; 58,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,48; 85,81</t>
+          <t>-42,65; 88,31</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,23</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,74</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,99</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,78</t>
+          <t>2,14</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 6,33</t>
+          <t>-2,32; 5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,12</t>
+          <t>-4,39; 3,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,61</t>
+          <t>-3,16; 6,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 5,43</t>
+          <t>-1,72; 6,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 3,22</t>
+          <t>0,97; 9,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,48</t>
+          <t>-1,77; 6,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,67</t>
+          <t>-1,11; 4,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,57</t>
+          <t>-1,08; 4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,57</t>
+          <t>-1,37; 4,72</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-8,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>35,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>74,7%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>16,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 132,62</t>
+          <t>-23,66; 88,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 191,09</t>
+          <t>-46,17; 55,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 139,72</t>
+          <t>-34,57; 93,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 91,2</t>
+          <t>-21,25; 131,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 53,83</t>
+          <t>9,89; 190,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 86,69</t>
+          <t>-25,11; 148,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 78,08</t>
+          <t>-13,99; 78,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 75,22</t>
+          <t>-11,89; 75,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 72,95</t>
+          <t>-17,49; 78,09</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,21</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,06</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,04</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 6,01</t>
+          <t>-5,72; 3,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,12</t>
+          <t>-4,17; 5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,26</t>
+          <t>-5,38; 4,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 4,78</t>
+          <t>-4,99; 5,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 5,18</t>
+          <t>-7,63; 2,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 4,49</t>
+          <t>-5,83; 5,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,43</t>
+          <t>-3,94; 3,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 3,08</t>
+          <t>-4,07; 2,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,64</t>
+          <t>-3,68; 3,75</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,48%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5,92%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-24,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,48%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0,62%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 115,1</t>
+          <t>-59,82; 82,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,11; 65,41</t>
+          <t>-43,58; 140,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 99,27</t>
+          <t>-54,25; 106,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 112,39</t>
+          <t>-45,91; 115,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 112,14</t>
+          <t>-64,4; 53,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 107,76</t>
+          <t>-48,43; 106,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 64,05</t>
+          <t>-41,0; 57,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,17; 56,06</t>
+          <t>-42,65; 46,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 63,89</t>
+          <t>-37,85; 62,25</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,55</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,91</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,83</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,55</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,91</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 4,9</t>
+          <t>0,77; 9,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 4,26</t>
+          <t>-2,37; 4,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 4,47</t>
+          <t>0,42; 8,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,94</t>
+          <t>-2,42; 5,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,56</t>
+          <t>-2,45; 4,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,06; 7,57</t>
+          <t>-1,38; 5,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,65</t>
+          <t>0,23; 5,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,44</t>
+          <t>-1,51; 3,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,23</t>
+          <t>0,53; 5,59</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>120,18%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>24,11%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>103,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>29,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>20,38%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>29,21%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>120,18%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,22; 222,9</t>
+          <t>4,6; 367,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,99; 176,44</t>
+          <t>-49,55; 199,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,64; 182,57</t>
+          <t>2,99; 340,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,43; 363,12</t>
+          <t>-44,27; 193,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,43; 196,89</t>
+          <t>-45,66; 168,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 327,18</t>
+          <t>-24,75; 219,5</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,94; 189,11</t>
+          <t>1,61; 187,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 119,21</t>
+          <t>-31,18; 120,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 178,38</t>
+          <t>6,03; 189,32</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,05</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>2,17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,48</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,66</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,56</t>
+          <t>-0,27; 4,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,81</t>
+          <t>-2,16; 1,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,67</t>
+          <t>-1,17; 3,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 4,06</t>
+          <t>-0,06; 4,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 2,03</t>
+          <t>-0,88; 3,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,65</t>
+          <t>-1,16; 3,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,63</t>
+          <t>0,61; 3,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,22</t>
+          <t>-0,95; 2,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,56</t>
+          <t>-0,33; 3,06</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,63%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-0,74%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>22,9%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,63%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-0,74%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 84,31</t>
+          <t>-4,72; 71,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 71,9</t>
+          <t>-28,71; 34,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 48,84</t>
+          <t>-15,48; 66,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 72,04</t>
+          <t>-1,3; 80,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 35,74</t>
+          <t>-11,39; 69,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 68,18</t>
+          <t>-15,97; 69,01</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,13; 61,11</t>
+          <t>7,62; 67,37</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 38,64</t>
+          <t>-13,13; 41,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 43,58</t>
+          <t>-5,75; 52,29</t>
         </is>
       </c>
     </row>
